--- a/dataproduct.api/wwwroot/templates/PKH_LFRH.xlsx
+++ b/dataproduct.api/wwwroot/templates/PKH_LFRH.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20730"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01AEA8F-80E3-47DD-8AAD-4DB586807F7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974E7449-FF98-4736-A84E-0AA41B88070D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <r>
       <t xml:space="preserve">BM.14/QT.05.15
@@ -86,6 +86,15 @@
     <t>Khối lượng thép lỏng (Tấn)
 (Tính cả thùng thép)</t>
   </si>
+  <si>
+    <t>Ngày</t>
+  </si>
+  <si>
+    <t>Ca</t>
+  </si>
+  <si>
+    <t>Kíp</t>
+  </si>
 </sst>
 </file>
 
@@ -174,7 +183,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -265,12 +274,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -284,48 +306,51 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -355,8 +380,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>311924</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>543245</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>158723</xdr:rowOff>
     </xdr:to>
@@ -796,93 +821,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8998A0CC-6572-4F8E-B67D-8241951B997E}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" customWidth="1"/>
-    <col min="2" max="3" width="10.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E1" s="9" t="s">
+    <row r="1" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="9"/>
+      <c r="I1" s="13"/>
     </row>
-    <row r="2" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+    <row r="2" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
     </row>
-    <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="2"/>
+    <row r="4" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:7" s="5" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:10" s="5" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:7" s="5" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:10" s="5" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="F6" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="G6" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="22"/>
-      <c r="F6" s="23"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:7" s="5" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="23"/>
+    <row r="7" spans="1:10" s="5" customFormat="1" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
     </row>
-    <row r="8" spans="1:7" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="20"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="E1:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
+  <mergeCells count="10">
+    <mergeCell ref="H1:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
